--- a/Antenna/Feed focus motor assembly/Parts list.xlsx
+++ b/Antenna/Feed focus motor assembly/Parts list.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jfrothingham/Code/Front-Page/Antenna/Feed focus motor assembly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BA856E-52A6-5844-82AD-B0429BF53E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F07221C-281D-9D45-B75D-250E2BB62AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52040" yWindow="600" windowWidth="20560" windowHeight="17180" xr2:uid="{5A00BFE3-024A-7848-AE3B-288923FA76A1}"/>
+    <workbookView xWindow="52040" yWindow="600" windowWidth="20560" windowHeight="17180" activeTab="1" xr2:uid="{5A00BFE3-024A-7848-AE3B-288923FA76A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="all parts" sheetId="1" r:id="rId1"/>
+    <sheet name="spares order" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="134">
   <si>
     <t>Feed focus motor assembly</t>
   </si>
@@ -74,21 +75,12 @@
     <t>SN32HRYY-LNK-NS-00</t>
   </si>
   <si>
-    <t>Same product may be branded Kollmorgen or Pacific Scientific.</t>
-  </si>
-  <si>
-    <t>iAutomation</t>
-  </si>
-  <si>
     <t>Pacific Scientific/Kollmorgen</t>
   </si>
   <si>
     <t>Order link</t>
   </si>
   <si>
-    <t>https://shop.iautomation.com/products/SN32HRYY-LNK-NS-00</t>
-  </si>
-  <si>
     <t xml:space="preserve">AC synchronous motor, 120Vac supply voltage, 0.47A rated current, 72rpm, 60Hz, NEMA 34 </t>
   </si>
   <si>
@@ -344,28 +336,123 @@
     <t>Read contact flat bracket</t>
   </si>
   <si>
-    <t>Read contact long bracket</t>
-  </si>
-  <si>
-    <t>Capacitor flanges</t>
-  </si>
-  <si>
     <t>Cover</t>
   </si>
   <si>
     <t>Plate</t>
+  </si>
+  <si>
+    <t>Metal half clamp</t>
+  </si>
+  <si>
+    <t>Capacitor flanges, secure cap to plate</t>
+  </si>
+  <si>
+    <t>Custom sheet metal to cover electronics</t>
+  </si>
+  <si>
+    <t>Custom sheet metal to hold electronics</t>
+  </si>
+  <si>
+    <t>Read contact post bracket</t>
+  </si>
+  <si>
+    <t>Hold read contact to plate (inside cover)</t>
+  </si>
+  <si>
+    <t>Hold read contact to antenna</t>
+  </si>
+  <si>
+    <t>Larger cable clamp</t>
+  </si>
+  <si>
+    <t>Smaller cable clamp</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/8876T13/</t>
+  </si>
+  <si>
+    <t>8876T13</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Cost ea.</t>
+  </si>
+  <si>
+    <t>AC synchronous motor</t>
+  </si>
+  <si>
+    <t>Wirewound resistor</t>
+  </si>
+  <si>
+    <t>Motor run capacitor</t>
+  </si>
+  <si>
+    <t>Wiring</t>
+  </si>
+  <si>
+    <t>Spare assembly and retrofitting, October 2026</t>
+  </si>
+  <si>
+    <t>Order cost:</t>
+  </si>
+  <si>
+    <t>See attached quote</t>
+  </si>
+  <si>
+    <t>Mfg. part #</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>Might have some on-hand</t>
+  </si>
+  <si>
+    <t>Cannot find exact size, is it custom? Might have some on-hand</t>
+  </si>
+  <si>
+    <t>Ferrules, 20AWG</t>
+  </si>
+  <si>
+    <t>Eye crimps, 20AWG</t>
+  </si>
+  <si>
+    <t>Ground wires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure connections to terminal </t>
+  </si>
+  <si>
+    <t>Assume on-hand</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/276829447492; https://www.ebay.com/itm/277300786756</t>
+  </si>
+  <si>
+    <t>Wake Industrial, eBay</t>
+  </si>
+  <si>
+    <t>Same product may be branded Kollmorgen or Pacific Scientific. No longer made. Some available through Wake Automation. Found some available on eBay.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="173" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -380,6 +467,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -403,13 +495,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -745,25 +841,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F2D2B6-6C97-9C4C-9FCD-6CBAAE6991DF}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.5" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.5" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>46297</v>
       </c>
     </row>
@@ -772,629 +869,1074 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
       <c r="H4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I4" t="s">
         <v>11</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>590</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" t="s">
-        <v>12</v>
-      </c>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5">
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>4.88</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="D6">
+      <c r="J6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>14.82</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
         <v>67</v>
       </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="H7" t="s">
         <v>68</v>
       </c>
-      <c r="D7">
+      <c r="I7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>15.65</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
       <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8">
         <v>100</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
         <v>1</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <v>0.76</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10">
+        <v>28</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10">
         <v>100</v>
       </c>
-      <c r="J10" s="5">
+      <c r="K10" s="5">
         <v>7.9799999999999996E-2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11">
+        <v>28</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11">
         <v>100</v>
       </c>
-      <c r="J11" s="5">
+      <c r="K11" s="5">
         <v>0.14649999999999999</v>
-      </c>
-      <c r="L11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12">
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12">
         <v>4</v>
       </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12">
+        <v>28</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12">
         <v>100</v>
       </c>
-      <c r="J12" s="5">
+      <c r="K12" s="5">
         <v>0.15329999999999999</v>
-      </c>
-      <c r="L12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13">
+        <v>28</v>
+      </c>
+      <c r="I13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13">
         <v>50</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
         <v>57</v>
       </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" t="s">
-        <v>31</v>
-      </c>
       <c r="H14" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14">
+        <v>28</v>
+      </c>
+      <c r="I14" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14">
         <v>100</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <v>6.2E-2</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" t="s">
-        <v>31</v>
-      </c>
       <c r="H15" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15">
+        <v>28</v>
+      </c>
+      <c r="I15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15">
         <v>100</v>
       </c>
-      <c r="J15" s="5">
+      <c r="K15" s="5">
         <v>4.8800000000000003E-2</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.12189999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
         <v>78</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
         <v>79</v>
       </c>
-      <c r="D16">
+      <c r="H17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17">
+        <v>50</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0.1162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="I16">
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18">
+        <v>79205</v>
+      </c>
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18">
         <v>1</v>
       </c>
-      <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17">
+      <c r="K18" s="5">
+        <v>20.55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17">
+      <c r="F19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19">
+        <v>40.112000000000002</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>89</v>
+      </c>
+      <c r="J19">
         <v>50</v>
       </c>
-      <c r="J17" s="5">
-        <v>0.1162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18">
+      <c r="K19" s="5">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18">
-        <v>79205</v>
-      </c>
-      <c r="G18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I18">
+      <c r="F20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
+        <v>95</v>
+      </c>
+      <c r="J20">
         <v>1</v>
       </c>
-      <c r="J18" s="5">
-        <v>20.55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19">
-        <v>40.112000000000002</v>
-      </c>
-      <c r="G19" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19">
-        <v>50</v>
-      </c>
-      <c r="J19" s="5">
-        <v>9.8000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="K20" s="5">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
         <v>96</v>
       </c>
-      <c r="F20" t="s">
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s">
         <v>97</v>
       </c>
-      <c r="G20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>98</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20" s="5">
-        <v>12.05</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+      <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
+        <v>125</v>
+      </c>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="5"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>100</v>
       </c>
-      <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>101</v>
-      </c>
-      <c r="J23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>102</v>
-      </c>
-      <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>103</v>
-      </c>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="B27" t="s">
         <v>104</v>
       </c>
-      <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>105</v>
-      </c>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="L28" t="s">
-        <v>62</v>
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{64549293-7E74-294E-86FA-2DE1782797F4}"/>
+    <hyperlink ref="D4" r:id="rId1" display="https://shop.iautomation.com/products/SN32HRYY-LNK-NS-00" xr:uid="{64549293-7E74-294E-86FA-2DE1782797F4}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{EA164E27-8547-6046-B9A6-E95159A334D4}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{4905A8F7-0100-F148-BCEF-51DD55ABC47B}"/>
+    <hyperlink ref="D7" r:id="rId4" xr:uid="{B2B3DD30-6251-F540-8ABA-779E732CDAAD}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{EBF6C933-3E05-8F41-A2B3-147668113548}"/>
+    <hyperlink ref="D20" r:id="rId6" xr:uid="{91B52DA7-6332-7148-BDD7-1AE836F5A8A8}"/>
+    <hyperlink ref="D18" r:id="rId7" xr:uid="{EBE5EF90-C502-9B4D-AC05-38B5B786CF88}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304FAF57-B005-DF4F-A8B9-5B409C1BDD2E}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.5" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1">
+        <f>SUM(F4:F15)</f>
+        <v>2423.48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>489</v>
+      </c>
+      <c r="F4">
+        <f>D4*E4</f>
+        <v>1956</v>
+      </c>
+      <c r="G4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>4.88</v>
+      </c>
+      <c r="F5">
+        <f>D5*E5</f>
+        <v>97.6</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>14.82</v>
+      </c>
+      <c r="F6">
+        <f>D6*E6</f>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>15.65</v>
+      </c>
+      <c r="F7">
+        <f>D7*E7</f>
+        <v>78.25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8" s="9">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="F8">
+        <f>D8*E8</f>
+        <v>9.9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.14649999999999999</v>
+      </c>
+      <c r="F9">
+        <f t="shared" ref="F9:F12" si="0">D9*E9</f>
+        <v>14.649999999999999</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>14.000000000000002</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>6.2E-2</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>6.2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>4.88</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>79205</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>20.55</v>
+      </c>
+      <c r="F13">
+        <f>D13*E13</f>
+        <v>102.75</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>12.05</v>
+      </c>
+      <c r="F14">
+        <f>D14*E14</f>
+        <v>60.25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15">
+        <v>40.112000000000002</v>
+      </c>
+      <c r="D15">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F15">
+        <f>D15*E15</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L19" s="5"/>
+    </row>
+    <row r="29" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="5"/>
+    </row>
+    <row r="31" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="5"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{7F0480D5-ACE0-9042-9B61-C355DED5AB21}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{D7D7CC7D-E0CA-0145-AAD7-7AA19E598244}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
